--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gurleen kaur\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8078B1F-2F99-4148-9B91-CDEA3AF8DDAF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,15 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Gurleen kaur</t>
+  </si>
+  <si>
+    <t>september</t>
+  </si>
+  <si>
+    <t>MCA</t>
   </si>
 </sst>
 </file>
@@ -894,26 +903,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>57</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12628811</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>59</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>58</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1041,21 +1058,21 @@
         <v>120</v>
       </c>
       <c r="F7" s="14">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="G7" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" s="14">
         <v>45</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>945</v>
+        <v>1075</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>495</v>
+        <v>365</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>54</v>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8078B1F-2F99-4148-9B91-CDEA3AF8DDAF}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024F1557-3F74-41E2-AEB5-7D931FA5BCE2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,15 @@
   </si>
   <si>
     <t>MCA</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>not bad</t>
   </si>
 </sst>
 </file>
@@ -1083,29 +1092,55 @@
       <c r="M7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>140</v>
+      </c>
+      <c r="E8" s="14">
+        <v>130</v>
+      </c>
+      <c r="F8" s="14">
+        <v>100</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024F1557-3F74-41E2-AEB5-7D931FA5BCE2}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD44597E-9004-4540-860B-A5B91651846A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>not bad</t>
+  </si>
+  <si>
+    <t>perfect like me.</t>
   </si>
 </sst>
 </file>
@@ -1143,26 +1146,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B9" s="14">
+        <v>440</v>
+      </c>
+      <c r="C9" s="14">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14">
+        <v>200</v>
+      </c>
+      <c r="E9" s="14">
+        <v>100</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>50</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD44597E-9004-4540-860B-A5B91651846A}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CC18088-14FE-4ABB-A78E-2EC5EFA375FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>perfect like me.</t>
+  </si>
+  <si>
+    <t>felt beautifil.</t>
   </si>
 </sst>
 </file>
@@ -1192,26 +1195,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B10" s="14">
+        <v>450</v>
+      </c>
+      <c r="C10" s="14">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>150</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>70</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CC18088-14FE-4ABB-A78E-2EC5EFA375FD}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F862CE-656C-439B-A1C1-C1DAE9ABFB82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,15 @@
   </si>
   <si>
     <t>felt beautifil.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>downfall</t>
   </si>
 </sst>
 </file>
@@ -1241,26 +1250,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B11" s="14">
+        <v>500</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>20</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>20</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>860</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F862CE-656C-439B-A1C1-C1DAE9ABFB82}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA5D421-9A71-411E-B147-603AE10FEF1D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>downfall</t>
+  </si>
+  <si>
+    <t>gjust go with the flow</t>
   </si>
 </sst>
 </file>
@@ -1296,26 +1299,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B12" s="14">
+        <v>540</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>10</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA5D421-9A71-411E-B147-603AE10FEF1D}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D516A6-AF36-49B1-B933-D0CE455271BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,7 +243,16 @@
     <t>downfall</t>
   </si>
   <si>
-    <t>gjust go with the flow</t>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>just go with the flow</t>
+  </si>
+  <si>
+    <t>atleast I try.</t>
   </si>
 </sst>
 </file>
@@ -1341,30 +1350,54 @@
         <v>56</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B13" s="14">
+        <v>560</v>
+      </c>
+      <c r="C13" s="14">
+        <v>5</v>
+      </c>
+      <c r="D13" s="14">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14">
+        <v>70</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="0"/>
+        <v>765</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="1"/>
+        <v>675</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="L13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a78b312ff00cc90/Desktop/gunnu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D516A6-AF36-49B1-B933-D0CE455271BE}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{CFBC1DC7-826C-48C1-BFA7-7CF3E89A7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E986F96D-1CC5-4576-A17D-B10161D26504}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +254,12 @@
   </si>
   <si>
     <t>atleast I try.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>not bad but not good</t>
   </si>
 </sst>
 </file>
@@ -533,6 +540,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1400,26 +1411,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>100</v>
+      </c>
+      <c r="E14" s="14">
+        <v>100</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
